--- a/SAP Reports/Input Files/Bal-Sht Jan 26/BS ITCURVES JAN 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/Bal-Sht Jan 26/BS ITCURVES JAN 26 ANNUAL.xlsx
@@ -14,36 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="84">
   <si>
     <t>Account Name</t>
   </si>
   <si>
-    <t>Current Period</t>
-  </si>
-  <si>
-    <t>Comparison Period</t>
-  </si>
-  <si>
-    <t>Difference Amount</t>
-  </si>
-  <si>
-    <t>Percentage Difference</t>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>System Currency</t>
   </si>
   <si>
     <t>Assets</t>
   </si>
   <si>
-    <t>$  767,144.63</t>
-  </si>
-  <si>
-    <t>$  665,410.19</t>
-  </si>
-  <si>
-    <t>$ 101,734.44</t>
-  </si>
-  <si>
-    <t>% 15.289</t>
+    <t>$  769,769.63</t>
   </si>
   <si>
     <t>Current Assets - Cash and Equiv</t>
@@ -55,15 +40,6 @@
     <t>$  491,233.34</t>
   </si>
   <si>
-    <t>$  434,198.78</t>
-  </si>
-  <si>
-    <t>$ 57,034.56</t>
-  </si>
-  <si>
-    <t>% 13.136</t>
-  </si>
-  <si>
     <t>101000-04-000-00 - SSB BANK ACCOUNT</t>
   </si>
   <si>
@@ -79,42 +55,12 @@
     <t>Receivables - RECEIVABLES</t>
   </si>
   <si>
-    <t>$  222,375.19</t>
-  </si>
-  <si>
-    <t>$  165,175.31</t>
-  </si>
-  <si>
-    <t>$ 57,199.88</t>
-  </si>
-  <si>
-    <t>% 34.630</t>
+    <t>$  225,000.19</t>
   </si>
   <si>
     <t>110000-04-000-00 - CLIENT FEES RECEIVABLE</t>
   </si>
   <si>
-    <t>$  115,175.31</t>
-  </si>
-  <si>
-    <t>$ 107,199.88</t>
-  </si>
-  <si>
-    <t>% 93.075</t>
-  </si>
-  <si>
-    <t>120002-04-000-00 - LOAN THRU SISTER COMP</t>
-  </si>
-  <si>
-    <t>$  50,000.00</t>
-  </si>
-  <si>
-    <t>$ -50,000.00</t>
-  </si>
-  <si>
-    <t>% -100.000</t>
-  </si>
-  <si>
     <t>Total Receivables - RECEIVABLES</t>
   </si>
   <si>
@@ -130,15 +76,6 @@
     <t>$  53,536.10</t>
   </si>
   <si>
-    <t>$  66,036.10</t>
-  </si>
-  <si>
-    <t>$ -12,500.00</t>
-  </si>
-  <si>
-    <t>% -18.929</t>
-  </si>
-  <si>
     <t>133000-04-000-00 - Prepaid PTET: MD</t>
   </si>
   <si>
@@ -151,12 +88,6 @@
     <t>$  46,803.10</t>
   </si>
   <si>
-    <t>139600-00-000-00 - PREPAID NCS Offshore</t>
-  </si>
-  <si>
-    <t>$  12,500.00</t>
-  </si>
-  <si>
     <t>Total Other Current - OTHER CURRENT ASSETS</t>
   </si>
   <si>
@@ -223,30 +154,12 @@
     <t>$  54,142.04</t>
   </si>
   <si>
-    <t>$  65,107.48</t>
-  </si>
-  <si>
-    <t>$ -10,965.44</t>
-  </si>
-  <si>
-    <t>% -16.842</t>
-  </si>
-  <si>
     <t>Current Liabs - Current Liabilities</t>
   </si>
   <si>
     <t>$  53,892.46</t>
   </si>
   <si>
-    <t>$  64,690.39</t>
-  </si>
-  <si>
-    <t>$ -10,797.93</t>
-  </si>
-  <si>
-    <t>% -16.692</t>
-  </si>
-  <si>
     <t>Accts Payable - ACCOUNTS PAYABLE</t>
   </si>
   <si>
@@ -259,12 +172,6 @@
     <t>$ (2,431.04)</t>
   </si>
   <si>
-    <t>$  8,366.89</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
     <t>218000-04-000-00 - 401-K PAYABLE</t>
   </si>
   <si>
@@ -292,15 +199,6 @@
     <t>$  249.58</t>
   </si>
   <si>
-    <t>$  417.09</t>
-  </si>
-  <si>
-    <t>$ -167.51</t>
-  </si>
-  <si>
-    <t>% -40.162</t>
-  </si>
-  <si>
     <t>L/Term Liabs - Long Term Liabilities</t>
   </si>
   <si>
@@ -319,30 +217,15 @@
     <t>Equity</t>
   </si>
   <si>
-    <t>$  713,002.59</t>
+    <t>$  715,627.59</t>
+  </si>
+  <si>
+    <t>Stock Equity - Stockholders Equity</t>
   </si>
   <si>
     <t>$  600,302.71</t>
   </si>
   <si>
-    <t>$ 112,699.88</t>
-  </si>
-  <si>
-    <t>% 18.774</t>
-  </si>
-  <si>
-    <t>Stock Equity - Stockholders Equity</t>
-  </si>
-  <si>
-    <t>$  581,585.79</t>
-  </si>
-  <si>
-    <t>$ 18,716.92</t>
-  </si>
-  <si>
-    <t>% 3.218</t>
-  </si>
-  <si>
     <t>Common Stock - COMMON STOCK</t>
   </si>
   <si>
@@ -367,12 +250,6 @@
     <t>$ (190,325.39)</t>
   </si>
   <si>
-    <t>$ (209,042.31)</t>
-  </si>
-  <si>
-    <t>% 8.954</t>
-  </si>
-  <si>
     <t>390050-04-000-00 - RETAINED EARNINGS</t>
   </si>
   <si>
@@ -385,16 +262,7 @@
     <t>Profit Period</t>
   </si>
   <si>
-    <t>$  112,699.88</t>
-  </si>
-  <si>
-    <t>$  18,716.92</t>
-  </si>
-  <si>
-    <t>$ 93,982.96</t>
-  </si>
-  <si>
-    <t>% 502.128</t>
+    <t>$  115,324.88</t>
   </si>
   <si>
     <t>Total Equity</t>
@@ -1255,1194 +1123,980 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
 		</row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
 		</row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
 		</row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
 		</row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
 		</row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+		</row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+		</row>
+    <row r="22">
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+		</row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+		</row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20">
-		</row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22">
-		</row>
-    <row r="23">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26">
-		</row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28">
-		</row>
+    </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" t="s">
-        <v>40</v>
-      </c>
-    </row>
+		</row>
     <row r="34">
       <c r="B34" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
-		</row>
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-    </row>
+		</row>
     <row r="38">
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" t="s">
-        <v>19</v>
+      <c r="A38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39">
 		</row>
     <row r="40">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>27</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="41">
 		</row>
     <row r="42">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
-		</row>
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>52</v>
-      </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" t="s">
-        <v>51</v>
-      </c>
-    </row>
+		</row>
     <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
 		</row>
     <row r="50">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51">
-		</row>
+      <c r="A51" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" t="s">
-        <v>59</v>
-      </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
-        <v>63</v>
-      </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" t="s">
-        <v>19</v>
+      <c r="A56" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
-        <v>64</v>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="s">
+        <v>42</v>
+      </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
-        <v>65</v>
-      </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-    </row>
+		</row>
     <row r="64">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
 		</row>
     <row r="66">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" t="s">
-        <v>70</v>
-      </c>
-      <c r="E66" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67">
 		</row>
     <row r="68">
       <c r="A68" t="s">
-        <v>72</v>
-      </c>
-      <c r="B68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" t="s">
-        <v>75</v>
-      </c>
-      <c r="E68" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
 		</row>
     <row r="70">
-      <c r="A70" t="s">
-        <v>77</v>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="71">
-		</row>
+      <c r="A71" t="s">
+        <v>49</v>
+      </c>
+    </row>
     <row r="72">
       <c r="B72" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
-        <v>78</v>
-      </c>
-    </row>
+		</row>
     <row r="74">
+      <c r="A74" t="s">
+        <v>50</v>
+      </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75">
 		</row>
     <row r="76">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" t="s">
-        <v>75</v>
-      </c>
-      <c r="E76" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77">
-		</row>
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
-      </c>
-      <c r="D78" t="s">
-        <v>75</v>
-      </c>
-      <c r="E78" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" t="s">
-        <v>75</v>
-      </c>
-      <c r="E80" t="s">
-        <v>82</v>
-      </c>
-    </row>
+		</row>
     <row r="81">
+      <c r="A81" t="s">
+        <v>54</v>
+      </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82">
 		</row>
     <row r="83">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84">
-		</row>
+      <c r="B84" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" t="s">
-        <v>86</v>
-      </c>
-      <c r="C87" t="s">
-        <v>86</v>
-      </c>
-    </row>
+		</row>
     <row r="88">
       <c r="B88" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
-		</row>
+      <c r="A89" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="90">
       <c r="B90" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="s">
-        <v>89</v>
-      </c>
-      <c r="B91" t="s">
-        <v>73</v>
-      </c>
-      <c r="C91" t="s">
-        <v>74</v>
-      </c>
-      <c r="D91" t="s">
-        <v>75</v>
-      </c>
-      <c r="E91" t="s">
-        <v>76</v>
-      </c>
-    </row>
+		</row>
     <row r="92">
+      <c r="A92" t="s">
+        <v>59</v>
+      </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93">
-		</row>
+      <c r="A93" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="94">
-      <c r="A94" t="s">
-        <v>90</v>
-      </c>
-      <c r="B94" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" t="s">
-        <v>92</v>
-      </c>
-      <c r="D94" t="s">
-        <v>93</v>
-      </c>
-      <c r="E94" t="s">
-        <v>94</v>
-      </c>
-    </row>
+		</row>
     <row r="95">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96">
 		</row>
     <row r="97">
-      <c r="A97" t="s">
-        <v>96</v>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="98">
-		</row>
+      <c r="A98" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="99">
       <c r="B99" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="s">
-        <v>97</v>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="s">
-        <v>19</v>
-      </c>
-      <c r="C101" t="s">
-        <v>19</v>
+      <c r="A101" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s">
-        <v>98</v>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
       <c r="B104" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C104" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="s">
+        <v>66</v>
+      </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
-        <v>99</v>
-      </c>
-      <c r="B106" t="s">
-        <v>68</v>
-      </c>
-      <c r="C106" t="s">
-        <v>69</v>
-      </c>
-      <c r="D106" t="s">
-        <v>70</v>
-      </c>
-      <c r="E106" t="s">
-        <v>71</v>
-      </c>
-    </row>
+		</row>
     <row r="107">
       <c r="A107" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C107" t="s">
-        <v>102</v>
-      </c>
-      <c r="D107" t="s">
-        <v>103</v>
-      </c>
-      <c r="E107" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108">
 		</row>
     <row r="109">
       <c r="A109" t="s">
-        <v>105</v>
-      </c>
-      <c r="B109" t="s">
-        <v>102</v>
-      </c>
-      <c r="C109" t="s">
-        <v>106</v>
-      </c>
-      <c r="D109" t="s">
-        <v>107</v>
-      </c>
-      <c r="E109" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110">
 		</row>
     <row r="111">
-      <c r="A111" t="s">
-        <v>109</v>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="112">
-		</row>
+      <c r="A112" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="113">
       <c r="B113" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
-        <v>110</v>
-      </c>
-    </row>
+		</row>
     <row r="115">
+      <c r="A115" t="s">
+        <v>72</v>
+      </c>
       <c r="B115" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
 		</row>
     <row r="117">
       <c r="A117" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C117" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118">
-		</row>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="B119" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C119" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
-        <v>114</v>
-      </c>
-      <c r="B121" t="s">
-        <v>112</v>
-      </c>
-      <c r="C121" t="s">
-        <v>112</v>
-      </c>
-    </row>
+		</row>
     <row r="122">
+      <c r="A122" t="s">
+        <v>76</v>
+      </c>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123">
 		</row>
     <row r="124">
       <c r="A124" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="B124" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>117</v>
-      </c>
-      <c r="D124" t="s">
-        <v>107</v>
-      </c>
-      <c r="E124" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="125">
-		</row>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="B126" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
-      </c>
-      <c r="D126" t="s">
-        <v>107</v>
-      </c>
-      <c r="E126" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
-        <v>120</v>
-      </c>
       <c r="B128" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>117</v>
-      </c>
-      <c r="D128" t="s">
-        <v>107</v>
-      </c>
-      <c r="E128" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="s">
+        <v>80</v>
+      </c>
       <c r="B129" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C129" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="B131" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C131" t="s">
-        <v>106</v>
-      </c>
-      <c r="D131" t="s">
-        <v>107</v>
-      </c>
-      <c r="E131" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="B133" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C133" t="s">
-        <v>124</v>
-      </c>
-      <c r="D133" t="s">
-        <v>125</v>
-      </c>
-      <c r="E133" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
-        <v>127</v>
-      </c>
       <c r="B135" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>102</v>
-      </c>
-      <c r="D135" t="s">
-        <v>103</v>
-      </c>
-      <c r="E135" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C136" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="s">
-        <v>6</v>
-      </c>
-      <c r="C137" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" t="s">
-        <v>66</v>
-      </c>
-      <c r="C138" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="139">
 		</row>
   </sheetData>
 </worksheet>
